--- a/psy-knowledge-graph/data/knowledge-graph-source.xlsx
+++ b/psy-knowledge-graph/data/knowledge-graph-source.xlsx
@@ -13866,7 +13866,7 @@
       </c>
       <c r="B175" s="5" t="inlineStr">
         <is>
-          <t>经验主义（Excel测试✅已生效）</t>
+          <t>经验主义</t>
         </is>
       </c>
       <c r="C175" s="5" t="inlineStr">
